--- a/tasks/finalpool/pw-sf-support-escalation-excel-email-gcal/groundtruth_workspace/Support_Escalation_Report.xlsx
+++ b/tasks/finalpool/pw-sf-support-escalation-excel-email-gcal/groundtruth_workspace/Support_Escalation_Report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,27 +440,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ticket_Count</t>
+          <t>Our_Avg_Response</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Our_Avg_Response</t>
+          <t>Industry_Avg</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Industry_Avg</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>Gap</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CSAT</t>
         </is>
       </c>
     </row>
@@ -471,19 +461,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6466</v>
+        <v>6.23</v>
       </c>
       <c r="C2" t="n">
-        <v>6.23</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
         <v>1.25</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.26</v>
       </c>
     </row>
     <row r="3">
@@ -493,19 +477,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9348</v>
+        <v>25.76</v>
       </c>
       <c r="C3" t="n">
-        <v>25.76</v>
+        <v>20.6</v>
       </c>
       <c r="D3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E3" t="n">
         <v>5.15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -515,19 +493,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15774</v>
+        <v>12.28</v>
       </c>
       <c r="C4" t="n">
-        <v>12.28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E4" t="n">
         <v>2.46</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.26</v>
       </c>
     </row>
   </sheetData>
